--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117683256</v>
       </c>
       <c r="B2" t="n">
-        <v>97754</v>
+        <v>97756</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>118669849</v>
       </c>
       <c r="B3" t="n">
-        <v>97883</v>
+        <v>97890</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -924,6 +924,138 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123522514</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57487</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bengts 1:29 6, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>734004</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6369838</v>
+      </c>
+      <c r="S4" t="n">
+        <v>54</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>123522514</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>123522514</v>
       </c>
       <c r="B4" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>123522514</v>
       </c>
       <c r="B4" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,6 +1056,130 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124837581</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57519</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bengts 1:29, Rodarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>733953</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6369982</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1061,7 +1061,7 @@
         <v>124837581</v>
       </c>
       <c r="B5" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1063,11 +1063,6 @@
       <c r="B5" t="n">
         <v>57648</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1175,6 +1175,474 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126159985</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östergarn Bengts 1:29, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>733994</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6369929</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I äldre skog på fuktig/blöt mark.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126160490</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98341</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Östergarn Bengts 1:29, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>733994</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6369929</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I äldre skog på fuktig/blöt mark.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126160005</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Östergarn Bengts 1:29, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>733994</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6369929</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I äldre skog på fuktig/blöt mark.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126160185</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98317</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Östergarn Bengts 1:29, Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>733994</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6369929</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I äldre skog på fuktig/blöt mark.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>126159985</v>
       </c>
       <c r="B6" t="n">
-        <v>98373</v>
+        <v>98375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>126160490</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>126160005</v>
       </c>
       <c r="B8" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126160185</v>
       </c>
       <c r="B9" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>126159985</v>
       </c>
       <c r="B6" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>126160490</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>126160005</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126160185</v>
       </c>
       <c r="B9" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>126159985</v>
       </c>
       <c r="B6" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>126160490</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>126160005</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126160185</v>
       </c>
       <c r="B9" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>126159985</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>126160490</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>126160005</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126160185</v>
       </c>
       <c r="B9" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1180,7 +1180,7 @@
         <v>126159985</v>
       </c>
       <c r="B6" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>126160490</v>
       </c>
       <c r="B7" t="n">
-        <v>98351</v>
+        <v>98354</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>126160005</v>
       </c>
       <c r="B8" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126160185</v>
       </c>
       <c r="B9" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1180,7 +1180,7 @@
         <v>126159985</v>
       </c>
       <c r="B6" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>126160490</v>
       </c>
       <c r="B7" t="n">
-        <v>98354</v>
+        <v>98363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         <v>126160005</v>
       </c>
       <c r="B8" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>126160185</v>
       </c>
       <c r="B9" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1643,6 +1643,244 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126493388</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98398</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219875</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönvit nattviol</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platanthera chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Östergarn Bengts 1:29, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>733994</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6369929</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ett tiotal plantor. I barrskog på fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126493541</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Östergarn Bengts 1:29, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>733994</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6369929</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fem plantor. I barrskog på fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,6 +1881,367 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131996758</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57903</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bengts 1:29, Rodarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>733953</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6369982</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131996762</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58304</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bengts 1:29, Rodarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>733953</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6369982</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131996767</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58344</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bengts 1:29, Rodarve, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>733953</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6369982</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jim Sundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1886,7 +1886,7 @@
         <v>131996758</v>
       </c>
       <c r="B12" t="n">
-        <v>57903</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>131996762</v>
       </c>
       <c r="B13" t="n">
-        <v>58304</v>
+        <v>58305</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>131996767</v>
       </c>
       <c r="B14" t="n">
-        <v>58344</v>
+        <v>58345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1886,7 +1886,7 @@
         <v>131996758</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>131996762</v>
       </c>
       <c r="B13" t="n">
-        <v>58305</v>
+        <v>58310</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>131996767</v>
       </c>
       <c r="B14" t="n">
-        <v>58345</v>
+        <v>58350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -2005,7 +2005,7 @@
         <v>131996762</v>
       </c>
       <c r="B13" t="n">
-        <v>58346</v>
+        <v>58348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>131996767</v>
       </c>
       <c r="B14" t="n">
-        <v>58386</v>
+        <v>58388</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1886,7 +1886,7 @@
         <v>131996758</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>131996762</v>
       </c>
       <c r="B13" t="n">
-        <v>58348</v>
+        <v>58349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>131996767</v>
       </c>
       <c r="B14" t="n">
-        <v>58388</v>
+        <v>58389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -1886,7 +1886,7 @@
         <v>131996758</v>
       </c>
       <c r="B12" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>131996762</v>
       </c>
       <c r="B13" t="n">
-        <v>58349</v>
+        <v>58353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>131996767</v>
       </c>
       <c r="B14" t="n">
-        <v>58389</v>
+        <v>58393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,73 +675,68 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117683256</v>
+        <v>123522514</v>
       </c>
       <c r="B2" t="n">
-        <v>97756</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bengts 1:29, Rodarve, Gtl</t>
+          <t>Bengts 1:29 6, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733953</v>
+        <v>734004</v>
       </c>
       <c r="R2" t="n">
-        <v>6369982</v>
+        <v>6369838</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,12 +760,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -798,69 +802,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118669849</v>
+        <v>124837581</v>
       </c>
       <c r="B3" t="n">
-        <v>97895</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bengts 1:29 6, Gtl</t>
+          <t>Bengts 1:29, Rodarve, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734004</v>
+        <v>733953</v>
       </c>
       <c r="R3" t="n">
-        <v>6369838</v>
+        <v>6369982</v>
       </c>
       <c r="S3" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +879,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,32 +921,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123522514</v>
+        <v>131996758</v>
       </c>
       <c r="B4" t="n">
-        <v>57519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,16 +954,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -982,17 +964,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bengts 1:29 6, Gtl</t>
+          <t>Bengts 1:29, Rodarve, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734004</v>
+        <v>733953</v>
       </c>
       <c r="R4" t="n">
-        <v>6369838</v>
+        <v>6369982</v>
       </c>
       <c r="S4" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,7 +998,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1026,12 +1008,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,27 +1040,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124837581</v>
+        <v>117169351</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>100094</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sommargylling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Oriolus oriolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1095,23 +1077,23 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bengts 1:29, Rodarve, Gtl</t>
+          <t>Sysnehagen, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>733953</v>
+        <v>733930</v>
       </c>
       <c r="R5" t="n">
-        <v>6369982</v>
+        <v>6369859</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1135,22 +1117,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,61 +1147,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jim Sundberg</t>
+          <t>Staffan Bergsmark</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jim Sundberg</t>
+          <t>Staffan Bergsmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126159985</v>
+        <v>131996767</v>
       </c>
       <c r="B6" t="n">
-        <v>98395</v>
+        <v>58415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östergarn Bengts 1:29, Gtl</t>
+          <t>Bengts 1:29, Rodarve, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>733994</v>
+        <v>733953</v>
       </c>
       <c r="R6" t="n">
-        <v>6369929</v>
+        <v>6369982</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1246,27 +1236,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I äldre skog på fuktig/blöt mark.</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,68 +1260,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
+          <t>Jim Sundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
+          <t>Jim Sundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126160490</v>
+        <v>131996762</v>
       </c>
       <c r="B7" t="n">
-        <v>98363</v>
+        <v>58375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219811</v>
+        <v>103037</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östergarn Bengts 1:29, Gtl</t>
+          <t>Bengts 1:29, Rodarve, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>733994</v>
+        <v>733953</v>
       </c>
       <c r="R7" t="n">
-        <v>6369929</v>
+        <v>6369982</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1363,27 +1359,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I äldre skog på fuktig/blöt mark.</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,29 +1383,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
+          <t>Jim Sundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Bolander</t>
+          <t>Jim Sundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126160005</v>
+        <v>126160185</v>
       </c>
       <c r="B8" t="n">
-        <v>98384</v>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,21 +1412,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1528,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126160185</v>
+        <v>126160490</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>99120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,21 +1529,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>219811</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1645,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126493388</v>
+        <v>126160005</v>
       </c>
       <c r="B10" t="n">
-        <v>98398</v>
+        <v>99142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,28 +1646,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219875</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1718,27 +1704,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ett tiotal plantor. I barrskog på fuktig mark.</t>
+          <t>I äldre skog på fuktig/blöt mark.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126493541</v>
+        <v>126159985</v>
       </c>
       <c r="B11" t="n">
-        <v>98279</v>
+        <v>99153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,21 +1763,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223591</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1835,27 +1821,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fem plantor. I barrskog på fuktig mark.</t>
+          <t>I äldre skog på fuktig/blöt mark.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,60 +1869,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131996758</v>
+        <v>118669849</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>99156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>219875</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bengts 1:29, Rodarve, Gtl</t>
+          <t>Bengts 1:29 6, Gtl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>733953</v>
+        <v>734004</v>
       </c>
       <c r="R12" t="n">
-        <v>6369982</v>
+        <v>6369838</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1960,22 +1950,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,61 +1992,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131996762</v>
+        <v>126493388</v>
       </c>
       <c r="B13" t="n">
-        <v>58353</v>
+        <v>99156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103037</v>
+        <v>219875</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bengts 1:29, Rodarve, Gtl</t>
+          <t>Östergarn Bengts 1:29, Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>733953</v>
+        <v>733994</v>
       </c>
       <c r="R13" t="n">
-        <v>6369982</v>
+        <v>6369929</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2083,22 +2065,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ett tiotal plantor. I barrskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,65 +2094,74 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jim Sundberg</t>
+          <t>Sebastian Bolander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jim Sundberg</t>
+          <t>Sebastian Bolander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131996767</v>
+        <v>117683256</v>
       </c>
       <c r="B14" t="n">
-        <v>58393</v>
+        <v>99036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102999</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bengts 1:29, Rodarve, Gtl</t>
@@ -2202,22 +2198,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>07:01</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>07:01</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2226,6 +2212,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2241,6 +2228,123 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126493541</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Östergarn Bengts 1:29, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>733994</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6369929</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Östergarn</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fem plantor. I barrskog på fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27280-2023 artfynd.xlsx
+++ b/artfynd/A 27280-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123522514</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124837581</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996758</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117169351</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1275,6 +1300,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1398,6 +1428,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996762</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1515,6 +1550,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126160185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1632,6 +1672,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126160490</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1749,6 +1794,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126160005</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1866,6 +1916,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126159985</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1989,6 +2044,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118669849</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2110,6 +2170,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493388</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2228,6 +2293,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683256</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2345,8 +2415,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126493541</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>